--- a/source/out25/results/result_llm/result_20251024_134734_analisado_gabarito.xlsx
+++ b/source/out25/results/result_llm/result_20251024_134734_analisado_gabarito.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tcc-culturaeduca\source\out25\results\result_llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3188393F-3599-45D2-92DD-B6C625D8C90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EDFA80-9F28-444A-AEFF-AD84918932C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -861,9 +861,11 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="52.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.42578125" customWidth="1"/>
     <col min="6" max="6" width="33.5703125" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
